--- a/output/pdf_financials_xlsx/SYZ.xlsx
+++ b/output/pdf_financials_xlsx/SYZ.xlsx
@@ -1305,7 +1305,7 @@
         <v>4.373</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.541</v>
+        <v>-2.541</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>0.8169999999999999</v>
@@ -1597,7 +1597,7 @@
         <v>4.373</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.541</v>
+        <v>-2.541</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.727</v>
@@ -1774,7 +1774,7 @@
         <v>4.373</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.541</v>
+        <v>-2.541</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.727</v>
@@ -1955,7 +1955,7 @@
         <v>24.294444</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>23.1</v>
+        <v>-23.1</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>-14.54</v>
@@ -2016,7 +2016,7 @@
         <v>4.373</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.541</v>
+        <v>-2.541</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>0.8169999999999999</v>
@@ -2132,7 +2132,7 @@
         <v>11.064</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.541</v>
+        <v>-2.541</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>10.961</v>
@@ -2191,7 +2191,7 @@
         <v>28.6076276664512</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>3.682608695652174</v>
+        <v>-3.682608695652174</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>16.73077510150502</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>188.984088127295</v>
@@ -2309,7 +2309,7 @@
         <v>11.30704589528119</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>3.682608695652174</v>
+        <v>-3.682608695652174</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>-1.109686479225814</v>
@@ -3146,7 +3146,7 @@
         <v>3.307</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.268</v>
+        <v>4.02</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>3.792</v>
@@ -5529,49 +5529,49 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.000521</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.011544</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.014219</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.177</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.578</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.177</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.161</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>2.181</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>1.537</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>3.912</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>2.579</v>
       </c>
     </row>
     <row r="92">
@@ -5956,7 +5956,7 @@
         <v>4.373</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>2.541</v>
+        <v>-2.541</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-0.727</v>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10470,7 +10470,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -18010,7 +18014,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -27214,7 +27222,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -28540,7 +28552,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -57298,10 +57314,10 @@
         </is>
       </c>
       <c r="Q525" s="5" t="n">
-        <v>2.541</v>
+        <v>-2.541</v>
       </c>
       <c r="R525" s="5" t="n">
-        <v>1.1</v>
+        <v>-1.1</v>
       </c>
       <c r="S525" t="inlineStr">
         <is>
@@ -78106,10 +78122,10 @@
         </is>
       </c>
       <c r="I747" s="5" t="n">
-        <v>3.058</v>
+        <v>-3.058</v>
       </c>
       <c r="J747" s="5" t="n">
-        <v>2.548</v>
+        <v>-2.548</v>
       </c>
       <c r="K747" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SYZ.xlsx
+++ b/output/pdf_financials_xlsx/SYZ.xlsx
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>4.194</v>
+        <v>37.987</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>4.302</v>
+        <v>39.749</v>
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
         <v>43.554</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>35.337</v>
+        <v>1.544</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>34.244</v>
+        <v>-1.203</v>
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
@@ -1036,43 +1036,43 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.248656</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.224386</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.167929</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.176</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.398</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.235</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.198</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.332</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.666</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.401</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1983,43 +1983,43 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.894214</v>
+        <v>2.14287</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.031305</v>
+        <v>2.255691</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.285299</v>
+        <v>4.453228</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.058</v>
+        <v>3.234</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.548</v>
+        <v>2.946</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.636</v>
+        <v>6.871</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>7.219</v>
+        <v>7.417</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>13.172</v>
+        <v>13.504</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.009</v>
+        <v>10.675</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.924</v>
+        <v>2.325</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>4.373</v>
+        <v>4.388</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.541</v>
+        <v>-2.491</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-1.8</v>
@@ -2099,43 +2099,43 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.304034</v>
+        <v>2.55269</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.375769</v>
+        <v>2.600155</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.773046</v>
+        <v>4.940975</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.306</v>
+        <v>4.482</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.279</v>
+        <v>5.677</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>9.090999999999999</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>9.771000000000001</v>
+        <v>9.968999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>17.055</v>
+        <v>17.387</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>13.659</v>
+        <v>14.325</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6.154</v>
+        <v>6.555</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>11.064</v>
+        <v>11.079</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.541</v>
+        <v>-2.491</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>10.961</v>
+        <v>10.964</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>8.805999999999999</v>
@@ -2158,43 +2158,43 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>23.42024923087369</v>
+        <v>25.94780980192088</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>25.63694470276921</v>
+        <v>28.05829605219568</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>40.98696836494315</v>
+        <v>42.42900362095294</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>24.57341779375678</v>
+        <v>25.57781201848999</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19.30164533820841</v>
+        <v>20.75685557586838</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>25.35985271144834</v>
+        <v>26.01539834858291</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>29.67383381924198</v>
+        <v>30.27514577259475</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>44.65594888981986</v>
+        <v>45.52524088814411</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>36.31553759438477</v>
+        <v>38.08624906944592</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>16.16113868536464</v>
+        <v>17.21421255810289</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>28.6076276664512</v>
+        <v>28.64641241111829</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-3.682608695652174</v>
+        <v>-3.610144927536232</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>16.73077510150502</v>
+        <v>16.73535427542205</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>13.42398512172442</v>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -52866,7 +52866,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -56678,7 +56678,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -56776,7 +56776,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -60656,7 +60656,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -60754,7 +60754,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -63882,7 +63882,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -63976,7 +63976,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -66936,7 +66936,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -69342,7 +69342,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -72386,7 +72386,7 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -75332,7 +75332,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -77624,7 +77624,7 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -81146,7 +81146,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -86934,7 +86934,7 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
@@ -87032,7 +87032,7 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">

--- a/output/pdf_financials_xlsx/SYZ.xlsx
+++ b/output/pdf_financials_xlsx/SYZ.xlsx
@@ -2042,43 +2042,43 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.40982</v>
+        <v>0.520984</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.344464</v>
+        <v>0.421607</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.487747</v>
+        <v>0.563682</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.248</v>
+        <v>1.354</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.731</v>
+        <v>2.866</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2.455</v>
+        <v>2.584</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.552</v>
+        <v>2.702</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.883</v>
+        <v>4.025</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.65</v>
+        <v>3.742</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>4.23</v>
+        <v>0.038</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>6.691</v>
+        <v>0.061</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>10.144</v>
+        <v>0.198</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>10.606</v>
@@ -2099,43 +2099,43 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.55269</v>
+        <v>2.663854</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.600155</v>
+        <v>2.677298</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.940975</v>
+        <v>5.01691</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.482</v>
+        <v>4.588</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.677</v>
+        <v>5.812</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>9.326000000000001</v>
+        <v>9.455</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>9.968999999999999</v>
+        <v>10.119</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>17.387</v>
+        <v>17.529</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>14.325</v>
+        <v>14.417</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6.555</v>
+        <v>2.363</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>11.079</v>
+        <v>4.449</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.491</v>
+        <v>-2.318</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>10.964</v>
+        <v>1.018</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>8.805999999999999</v>
@@ -2158,43 +2158,43 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>25.94780980192088</v>
+        <v>27.07777949225568</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>28.05829605219568</v>
+        <v>28.89074686084152</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>42.42900362095294</v>
+        <v>43.08107054903031</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>25.57781201848999</v>
+        <v>26.18273126747703</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>20.75685557586838</v>
+        <v>21.25045703839123</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26.01539834858291</v>
+        <v>26.37525106003124</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>30.27514577259475</v>
+        <v>30.73068513119533</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>45.52524088814411</v>
+        <v>45.89704650188521</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.08624906944592</v>
+        <v>38.3308518557907</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>17.21421255810289</v>
+        <v>6.20552010294388</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>28.64641241111829</v>
+        <v>11.50355526826115</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-3.610144927536232</v>
+        <v>-3.359420289855072</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>16.73535427542205</v>
+        <v>1.553866349177275</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>13.42398512172442</v>
@@ -5982,43 +5982,43 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.526104</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.456156</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.621869</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2.937</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.676</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.783</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>4.082</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>4.297</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>10.144</v>
+        <v>0.198</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>10.606</v>
@@ -32908,7 +32908,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -34690,7 +34694,11 @@
           <t>Additions of intangible assets 8</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -36488,7 +36496,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -37672,7 +37684,11 @@
           <t>Additions of intangible assets 9</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -38500,7 +38516,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -39798,7 +39814,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -39888,7 +39908,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -43178,7 +43198,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -43274,7 +43298,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -44434,7 +44458,11 @@
           <t>Additions to intangible assets 11</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -45776,7 +45804,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -46726,7 +46758,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -46822,7 +46858,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -56108,7 +56144,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -60084,7 +60124,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
@@ -63428,7 +63472,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -66478,7 +66526,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E624" t="inlineStr">
         <is>
           <t>-</t>
@@ -66568,7 +66620,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -72000,7 +72052,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E683" t="inlineStr">
         <is>
           <t>-</t>
@@ -72096,7 +72152,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -74946,7 +75002,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E714" t="inlineStr">
         <is>
           <t>-</t>
@@ -75042,7 +75102,7 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -77238,7 +77298,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr">
         <is>
           <t>-</t>
@@ -77334,7 +77398,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -80568,7 +80632,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D773" t="inlineStr"/>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E773" t="inlineStr">
         <is>
           <t>-</t>
@@ -80664,7 +80732,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -83414,7 +83482,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E803" t="inlineStr">
         <is>
           <t>-</t>
@@ -83510,7 +83582,7 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -86262,7 +86334,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E833" t="inlineStr">
         <is>
           <t>-</t>
@@ -86358,7 +86434,7 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">

--- a/output/pdf_financials_xlsx/SYZ.xlsx
+++ b/output/pdf_financials_xlsx/SYZ.xlsx
@@ -2676,19 +2676,19 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.411271</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -2731,19 +2731,19 @@
         <v>1.769037</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.147991</v>
+        <v>2.559262</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.921</v>
+        <v>3.045</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3.111</v>
+        <v>3.222</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>5.013</v>
+        <v>6.043</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.492</v>
+        <v>3.717</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.317</v>
@@ -3116,19 +3116,19 @@
         <v>0.210641</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.297049</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.096</v>
+        <v>1.972</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.212</v>
+        <v>2.101</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.337</v>
+        <v>1.307</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.298</v>
+        <v>1.073</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>1.831</v>
@@ -4379,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.252</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
@@ -4434,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>18.21</v>
+        <v>18.462</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>21.21</v>
@@ -4654,10 +4654,10 @@
         <v>0.18</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.536</v>
+        <v>0.156</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.62</v>
+        <v>0.368</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>5.864</v>
@@ -4819,16 +4819,16 @@
         <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.491</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="P78" s="3" t="n">
         <v>0</v>
@@ -4874,16 +4874,16 @@
         <v>0</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.491</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="P79" s="3" t="n">
         <v>0</v>
@@ -4948,19 +4948,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.009600555212831586</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.3899858654216816</v>
+        <v>0.407589840236433</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.5315123418118031</v>
+        <v>0.5438165643403082</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.4577492885070618</v>
+        <v>0.4642125701518738</v>
       </c>
       <c r="P80" s="3" t="n">
         <v>0.5095649860316616</v>
@@ -5226,16 +5224,16 @@
         <v>2.351</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>2.442</v>
+        <v>2.324</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>11.565</v>
+        <v>10.995</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>12.246</v>
+        <v>11.755</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>12.932</v>
+        <v>12.689</v>
       </c>
       <c r="P85" s="3" t="n">
         <v>26.035</v>
@@ -6189,13 +6187,13 @@
         <v>-1.496</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>-0.301</v>
+        <v>-0.748</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="104">
@@ -6363,10 +6361,10 @@
         <v>9.702</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>6.415</v>
+        <v>6.576</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-1.555</v>
+        <v>-1.945</v>
       </c>
     </row>
     <row r="107">
@@ -6894,37 +6892,37 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.215244</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.08487699999999999</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.667</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.835</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.749</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.522</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.621</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.478</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.747</v>
       </c>
       <c r="N116" s="3" t="n">
         <v>0</v>
@@ -7185,10 +7183,10 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-2.097239</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-2.56354</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -7197,37 +7195,37 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-2.051</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-14.906</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-4.148</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-2.839</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-2.458</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.248</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-1.298</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.475</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-2.118</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="122">
@@ -17310,7 +17308,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -19600,7 +19602,11 @@
           <t>Lease obligations 15</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -20416,7 +20422,11 @@
           <t>Lease obligations 15</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -29680,7 +29690,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -31478,7 +31492,11 @@
           <t>Repurchase of common shares 13(c)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -35514,7 +35532,11 @@
           <t>Repurchase of common shares 15(e)</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -38250,7 +38272,11 @@
           <t>Repurchase of common shares 16(e)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -38888,7 +38914,11 @@
           <t>Acquisition of intangible assets 9</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -40646,7 +40676,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -46376,7 +46410,11 @@
           <t>Repurchase of common shares 11(e)</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -47244,7 +47282,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -47526,7 +47568,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
